--- a/output/pdf_financials_xlsx/ZEUS.xlsx
+++ b/output/pdf_financials_xlsx/ZEUS.xlsx
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.046175</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.363281</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.15066</v>
       </c>
     </row>
     <row r="119">
@@ -3878,7 +3878,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
         <v>-0.046175</v>
       </c>

--- a/output/pdf_financials_xlsx/ZEUS.xlsx
+++ b/output/pdf_financials_xlsx/ZEUS.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.08169700000000001</v>
+        <v>0.081772</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.5858409999999999</v>
+        <v>1.682997</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.47478</v>
+        <v>1.922856</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.08169700000000001</v>
+        <v>-0.081772</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.5858409999999999</v>
+        <v>-1.682997</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.47478</v>
+        <v>-1.922856</v>
       </c>
     </row>
     <row r="12">
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.167192</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.222711</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.256558</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.167192</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.222711</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.256558</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.167192</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.413509</v>
+        <v>0.190798</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.276533</v>
+        <v>0.019975</v>
       </c>
     </row>
     <row r="49">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4527,17 +4527,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>-0.081772</v>
+        <v>0.081772</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-1.682997</v>
+        <v>1.682997</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-1.922856</v>
+        <v>1.922856</v>
       </c>
     </row>
     <row r="61">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">

--- a/output/pdf_financials_xlsx/ZEUS.xlsx
+++ b/output/pdf_financials_xlsx/ZEUS.xlsx
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.00759</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.052162</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.025091</v>
       </c>
     </row>
     <row r="68">
@@ -2205,10 +2205,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.018131</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.005012</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -2224,10 +2224,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="112">
@@ -2610,10 +2610,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="135">
@@ -2626,10 +2626,10 @@
         <v>-0.079583</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.414329</v>
+        <v>-1.454329</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.305873</v>
+        <v>-1.310873</v>
       </c>
     </row>
   </sheetData>
@@ -3446,7 +3446,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.018131</v>
       </c>
@@ -3727,7 +3731,11 @@
           <t>Share issued for cash</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>0.3</v>
       </c>
@@ -3909,7 +3917,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
